--- a/artfynd/A 56737-2025 artfynd.xlsx
+++ b/artfynd/A 56737-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109733618</v>
+        <v>113178159</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gårdsjöberget, Jmt</t>
+          <t>SV om Läroverket, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528136.1734264047</v>
+        <v>528088</v>
       </c>
       <c r="R2" t="n">
-        <v>6985130.906398841</v>
+        <v>6985036</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,69 +754,80 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>ljus 130-årig tallskog på torr sandig mark</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter # rotben av gammal övermossad tallåga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113178159</v>
+        <v>129038521</v>
       </c>
       <c r="B3" t="n">
-        <v>78157</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>816</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smultronkantarell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Aphroditeola olida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>SV om Läroverket, Jmt</t>
+          <t>Läroverket, SV om, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528088</v>
+        <v>528080</v>
       </c>
       <c r="R3" t="n">
-        <v>6985036</v>
+        <v>6985105</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,15 +873,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>ljus 130-årig tallskog på torr sandig mark</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>1 substratenheter # rotben av gammal övermossad tallåga</t>
+          <t>äldre sandtallskog med fattigris och lav, plan mark med svallsediment</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -910,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129038520</v>
+        <v>129038522</v>
       </c>
       <c r="B4" t="n">
-        <v>92835</v>
+        <v>87412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,23 +906,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>3624</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528076</v>
+        <v>528204</v>
       </c>
       <c r="R4" t="n">
-        <v>6985103</v>
+        <v>6985204</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +975,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>äldre sandtallskog med fattigris och lav, plan mark med svallsediment</t>
+          <t>örtrik bäckkant i äldre barrnaturskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1016,32 +997,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129038523</v>
+        <v>129038517</v>
       </c>
       <c r="B5" t="n">
-        <v>92835</v>
+        <v>93191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528205</v>
+        <v>528020</v>
       </c>
       <c r="R5" t="n">
-        <v>6985194</v>
+        <v>6985018</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1081,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>slänt mot bäck i äldre sandtallskog, lingon</t>
+          <t>äldre sandtallskog med fattigris och lav, plan mark med svallsediment</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1122,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129038517</v>
+        <v>129038519</v>
       </c>
       <c r="B6" t="n">
-        <v>92829</v>
+        <v>93191</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528020</v>
+        <v>528056</v>
       </c>
       <c r="R6" t="n">
-        <v>6985018</v>
+        <v>6985072</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129038519</v>
+        <v>109733618</v>
       </c>
       <c r="B7" t="n">
-        <v>92829</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1239,34 +1220,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Läroverket, SV om, Jmt</t>
+          <t>Gårdsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528056</v>
+        <v>528136</v>
       </c>
       <c r="R7" t="n">
-        <v>6985072</v>
+        <v>6985131</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,12 +1277,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,57 +1291,53 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>äldre sandtallskog med fattigris och lav, plan mark med svallsediment</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Erik Söderhjelm</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129038522</v>
+        <v>129038518</v>
       </c>
       <c r="B8" t="n">
-        <v>87071</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3624</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1365,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528204</v>
+        <v>528029</v>
       </c>
       <c r="R8" t="n">
-        <v>6985204</v>
+        <v>6985046</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1394,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>örtrik bäckkant i äldre barrnaturskog</t>
+          <t>äldre sandtallskog med fattigris och lav, plan mark med svallsediment</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1436,14 +1416,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129038518</v>
+        <v>129038520</v>
       </c>
       <c r="B9" t="n">
-        <v>92835</v>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1471,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528029</v>
+        <v>528076</v>
       </c>
       <c r="R9" t="n">
-        <v>6985046</v>
+        <v>6985103</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,32 +1522,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129038521</v>
+        <v>129038523</v>
       </c>
       <c r="B10" t="n">
-        <v>88853</v>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>816</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smultronkantarell</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Aphroditeola olida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1577,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528080</v>
+        <v>528205</v>
       </c>
       <c r="R10" t="n">
-        <v>6985105</v>
+        <v>6985194</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,7 +1606,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>äldre sandtallskog med fattigris och lav, plan mark med svallsediment</t>
+          <t>slänt mot bäck i äldre sandtallskog, lingon</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1645,6 +1625,109 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>109733526</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gårdsjöberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>528303</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6985263</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56737-2025 artfynd.xlsx
+++ b/artfynd/A 56737-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178159</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129038521</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129038522</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129038517</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129038519</t>
         </is>
       </c>
     </row>
@@ -1307,6 +1337,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109733618</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1413,6 +1448,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129038518</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1519,6 +1559,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129038520</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1623,6 +1668,11 @@
       <c r="AY10" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129038523</t>
         </is>
       </c>
     </row>
@@ -1728,8 +1778,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109733526</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>